--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128609310</v>
+        <v>128612260</v>
       </c>
       <c r="B2" t="n">
         <v>79083</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462211</v>
+        <v>462213</v>
       </c>
       <c r="R2" t="n">
-        <v>6794680</v>
+        <v>6794674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128612260</v>
+        <v>128609310</v>
       </c>
       <c r="B3" t="n">
         <v>79083</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462213</v>
+        <v>462211</v>
       </c>
       <c r="R3" t="n">
-        <v>6794674</v>
+        <v>6794680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128609955</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128609955</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128609955</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128609955</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612260</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128610027</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128609985</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128611291</v>
       </c>
       <c r="B7" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128609310</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128609744</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128611999</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2025 artfynd.xlsx
+++ b/artfynd/A 39483-2025 artfynd.xlsx
@@ -1559,7 +1559,7 @@
         <v>128610340</v>
       </c>
       <c r="B10" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
